--- a/docs/qa/upload-templates/customer_master_upload_template.xlsx
+++ b/docs/qa/upload-templates/customer_master_upload_template.xlsx
@@ -133,17 +133,27 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Required</t>
+        <t>Required unique code</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>Required</t>
+        <t>Legal / trading name (required)</t>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
+    <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>A|B|C optional</t>
+        <t>A|B|C</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>ISO country or name (required)</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>USD|EGP|SAR|AED (required)</t>
       </text>
     </comment>
   </commentList>
@@ -439,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,12 +465,62 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>name_ar</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>tier</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>credit_limit</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>payment_terms</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>contact_name</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>contact_email</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>contact_phone</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>tax_id</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>active</t>
         </is>
       </c>
     </row>
@@ -472,16 +532,66 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Saudi Electricity</t>
+          <t>Saudi Electricity Company</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>الشركة السعودية للكهرباء</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
         <v>2000000</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Net30</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Omar Al-Harbi</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>omar@sec.example</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>+966500000001</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>SA-3001234567</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -497,11 +607,61 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>الكهرباء المصرية</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
         <v>1500000</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Net45</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Mona Hassan</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>mona@ee.example</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>+201000000002</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>EG-123456789</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -512,16 +672,66 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dubai Water</t>
+          <t>Dubai Water &amp; Electricity</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>مياه وكهرباء دبي</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>AED</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
         <v>500000</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Net30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Ali Rahman</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ali@dw.example</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>+971500000003</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>AE-987654321</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
       </c>
     </row>
   </sheetData>
